--- a/artfynd/A 35493-2026 artfynd.xlsx
+++ b/artfynd/A 35493-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137071086</v>
       </c>
       <c r="B2" t="n">
-        <v>92113</v>
+        <v>92114</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137071100</v>
       </c>
       <c r="B3" t="n">
-        <v>92113</v>
+        <v>92114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137071101</v>
       </c>
       <c r="B4" t="n">
-        <v>92113</v>
+        <v>92114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137071104</v>
       </c>
       <c r="B5" t="n">
-        <v>92113</v>
+        <v>92114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137071081</v>
       </c>
       <c r="B6" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>137071083</v>
       </c>
       <c r="B7" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>137071060</v>
       </c>
       <c r="B11" t="n">
-        <v>92344</v>
+        <v>92345</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>137071067</v>
       </c>
       <c r="B12" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>137071062</v>
       </c>
       <c r="B13" t="n">
-        <v>92113</v>
+        <v>92114</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>137071096</v>
       </c>
       <c r="B14" t="n">
-        <v>92113</v>
+        <v>92114</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>137071097</v>
       </c>
       <c r="B15" t="n">
-        <v>92113</v>
+        <v>92114</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>137071099</v>
       </c>
       <c r="B16" t="n">
-        <v>92113</v>
+        <v>92114</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
         <v>137071068</v>
       </c>
       <c r="B17" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>137071063</v>
       </c>
       <c r="B18" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>137071074</v>
       </c>
       <c r="B19" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>137071075</v>
       </c>
       <c r="B20" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>137071077</v>
       </c>
       <c r="B21" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>137071091</v>
       </c>
       <c r="B22" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3101,7 +3101,7 @@
         <v>137071093</v>
       </c>
       <c r="B23" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 35493-2026 artfynd.xlsx
+++ b/artfynd/A 35493-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ29"/>
+  <dimension ref="A1:AZ39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>137071086</v>
       </c>
       <c r="B2" t="n">
-        <v>92114</v>
+        <v>92120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137071100</v>
       </c>
       <c r="B3" t="n">
-        <v>92114</v>
+        <v>92120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137071101</v>
       </c>
       <c r="B4" t="n">
-        <v>92114</v>
+        <v>92120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137071104</v>
       </c>
       <c r="B5" t="n">
-        <v>92114</v>
+        <v>92120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,45 +1128,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>137071081</v>
+        <v>137133557</v>
       </c>
       <c r="B6" t="n">
-        <v>79483</v>
+        <v>92120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nygård, Jmt</t>
+          <t>Huug, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>430482</v>
+        <v>430724</v>
       </c>
       <c r="R6" t="n">
-        <v>7022553</v>
+        <v>7022456</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,27 +1193,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:07</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,51 +1234,51 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071081</t>
+          <t>https://artportalen.se/Sighting/137133557</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>137071083</v>
+        <v>137133560</v>
       </c>
       <c r="B7" t="n">
-        <v>79483</v>
+        <v>92120</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nygård, Jmt</t>
+          <t>Huug, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>430467</v>
+        <v>430731</v>
       </c>
       <c r="R7" t="n">
-        <v>7022533</v>
+        <v>7022448</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,27 +1305,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,16 +1346,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071083</t>
+          <t>https://artportalen.se/Sighting/137133560</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>137071084</v>
+        <v>137133561</v>
       </c>
       <c r="B8" t="n">
-        <v>58008</v>
+        <v>92120</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1373,39 +1363,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nygård, Jmt</t>
+          <t>Huug, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>430452</v>
+        <v>430722</v>
       </c>
       <c r="R8" t="n">
-        <v>7022519</v>
+        <v>7022447</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1432,27 +1417,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:09</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1478,16 +1458,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071084</t>
+          <t>https://artportalen.se/Sighting/137133561</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>137071087</v>
+        <v>137133562</v>
       </c>
       <c r="B9" t="n">
-        <v>58008</v>
+        <v>92120</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1495,39 +1475,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Nygård, Jmt</t>
+          <t>Huug, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>430569</v>
+        <v>430713</v>
       </c>
       <c r="R9" t="n">
-        <v>7022541</v>
+        <v>7022435</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1554,27 +1529,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Medelhögt livsmiljövärde</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1600,56 +1575,51 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071087</t>
+          <t>https://artportalen.se/Sighting/137133562</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>137071090</v>
+        <v>137071081</v>
       </c>
       <c r="B10" t="n">
-        <v>58008</v>
+        <v>79483</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Nygård, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>430574</v>
+        <v>430482</v>
       </c>
       <c r="R10" t="n">
-        <v>7022567</v>
+        <v>7022553</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1681,7 +1651,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1691,12 +1661,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Medelhögt livsmiljövärde</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1722,16 +1692,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071090</t>
+          <t>https://artportalen.se/Sighting/137071081</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>137071060</v>
+        <v>137071083</v>
       </c>
       <c r="B11" t="n">
-        <v>92345</v>
+        <v>79483</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1739,21 +1709,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>67</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1763,10 +1733,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>430482</v>
+        <v>430467</v>
       </c>
       <c r="R11" t="n">
-        <v>7022701</v>
+        <v>7022533</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1798,7 +1768,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1808,7 +1778,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1817,7 +1792,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1835,16 +1809,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071060</t>
+          <t>https://artportalen.se/Sighting/137071083</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>137071067</v>
+        <v>137071084</v>
       </c>
       <c r="B12" t="n">
-        <v>92389</v>
+        <v>58008</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1852,34 +1826,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Nygård, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>430555</v>
+        <v>430452</v>
       </c>
       <c r="R12" t="n">
-        <v>7022717</v>
+        <v>7022519</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1911,7 +1890,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1921,7 +1900,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1947,16 +1931,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071067</t>
+          <t>https://artportalen.se/Sighting/137071084</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>137071062</v>
+        <v>137071087</v>
       </c>
       <c r="B13" t="n">
-        <v>92114</v>
+        <v>58008</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1964,34 +1948,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Nygård, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>430537</v>
+        <v>430569</v>
       </c>
       <c r="R13" t="n">
-        <v>7022692</v>
+        <v>7022541</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2023,7 +2012,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2033,7 +2022,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2059,16 +2053,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071062</t>
+          <t>https://artportalen.se/Sighting/137071087</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>137071096</v>
+        <v>137071090</v>
       </c>
       <c r="B14" t="n">
-        <v>92114</v>
+        <v>58008</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2076,34 +2070,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Nygård, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>430876</v>
+        <v>430574</v>
       </c>
       <c r="R14" t="n">
-        <v>7022640</v>
+        <v>7022567</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2135,7 +2134,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2145,7 +2144,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Medelhögt livsmiljövärde</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2171,16 +2175,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071096</t>
+          <t>https://artportalen.se/Sighting/137071090</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>137071097</v>
+        <v>137133565</v>
       </c>
       <c r="B15" t="n">
-        <v>92114</v>
+        <v>58008</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2188,34 +2192,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Nygård, Jmt</t>
+          <t>Huug, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>430968</v>
+        <v>430720</v>
       </c>
       <c r="R15" t="n">
-        <v>7022619</v>
+        <v>7022370</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2242,22 +2251,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2283,16 +2297,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071097</t>
+          <t>https://artportalen.se/Sighting/137133565</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>137071099</v>
+        <v>137133566</v>
       </c>
       <c r="B16" t="n">
-        <v>92114</v>
+        <v>58008</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2300,34 +2314,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Nygård, Jmt</t>
+          <t>Huug, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>430958</v>
+        <v>430720</v>
       </c>
       <c r="R16" t="n">
-        <v>7022598</v>
+        <v>7022371</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2354,22 +2368,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2395,38 +2414,38 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071099</t>
+          <t>https://artportalen.se/Sighting/137133566</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>137071068</v>
+        <v>137071060</v>
       </c>
       <c r="B17" t="n">
-        <v>92118</v>
+        <v>92351</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>67</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2436,10 +2455,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>430554</v>
+        <v>430482</v>
       </c>
       <c r="R17" t="n">
-        <v>7022717</v>
+        <v>7022701</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2471,7 +2490,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2481,7 +2500,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2490,6 +2509,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2507,51 +2527,51 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071068</t>
+          <t>https://artportalen.se/Sighting/137071060</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>137071063</v>
+        <v>137133556</v>
       </c>
       <c r="B18" t="n">
-        <v>79483</v>
+        <v>89485</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Nygård, Jmt</t>
+          <t>Huug, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>430535</v>
+        <v>430671</v>
       </c>
       <c r="R18" t="n">
-        <v>7022722</v>
+        <v>7022733</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2578,27 +2598,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:44</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2624,38 +2639,38 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071063</t>
+          <t>https://artportalen.se/Sighting/137133556</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>137071074</v>
+        <v>137071067</v>
       </c>
       <c r="B19" t="n">
-        <v>79483</v>
+        <v>92395</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2665,10 +2680,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>430644</v>
+        <v>430555</v>
       </c>
       <c r="R19" t="n">
-        <v>7022665</v>
+        <v>7022717</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2700,7 +2715,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2710,12 +2725,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2741,38 +2751,38 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071074</t>
+          <t>https://artportalen.se/Sighting/137071067</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>137071075</v>
+        <v>137071062</v>
       </c>
       <c r="B20" t="n">
-        <v>79483</v>
+        <v>92120</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2782,10 +2792,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>430627</v>
+        <v>430537</v>
       </c>
       <c r="R20" t="n">
-        <v>7022606</v>
+        <v>7022692</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2817,7 +2827,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2827,12 +2837,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:01</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2858,38 +2863,38 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071075</t>
+          <t>https://artportalen.se/Sighting/137071062</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>137071077</v>
+        <v>137071096</v>
       </c>
       <c r="B21" t="n">
-        <v>79483</v>
+        <v>92120</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2899,10 +2904,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>430531</v>
+        <v>430876</v>
       </c>
       <c r="R21" t="n">
-        <v>7022585</v>
+        <v>7022640</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2934,7 +2939,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2944,12 +2949,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2975,38 +2975,38 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071077</t>
+          <t>https://artportalen.se/Sighting/137071096</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>137071091</v>
+        <v>137071097</v>
       </c>
       <c r="B22" t="n">
-        <v>79483</v>
+        <v>92120</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3016,10 +3016,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>430703</v>
+        <v>430968</v>
       </c>
       <c r="R22" t="n">
-        <v>7022632</v>
+        <v>7022619</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3061,12 +3061,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3092,38 +3087,38 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071091</t>
+          <t>https://artportalen.se/Sighting/137071097</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>137071093</v>
+        <v>137071099</v>
       </c>
       <c r="B23" t="n">
-        <v>79483</v>
+        <v>92120</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3133,10 +3128,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>430735</v>
+        <v>430958</v>
       </c>
       <c r="R23" t="n">
-        <v>7022634</v>
+        <v>7022598</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3168,7 +3163,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3178,12 +3173,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:27</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3209,51 +3199,51 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071093</t>
+          <t>https://artportalen.se/Sighting/137071099</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>137071076</v>
+        <v>137133551</v>
       </c>
       <c r="B24" t="n">
-        <v>58005</v>
+        <v>92120</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Nygård, Jmt</t>
+          <t>Huug, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>430579</v>
+        <v>430534</v>
       </c>
       <c r="R24" t="n">
-        <v>7022593</v>
+        <v>7022735</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3280,27 +3270,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:03</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Hack</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3326,16 +3311,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071076</t>
+          <t>https://artportalen.se/Sighting/137133551</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>137071092</v>
+        <v>137071068</v>
       </c>
       <c r="B25" t="n">
-        <v>58122</v>
+        <v>92124</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3343,42 +3328,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100090</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nucifraga caryocatactes</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Nygård, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>430711</v>
+        <v>430554</v>
       </c>
       <c r="R25" t="n">
-        <v>7022639</v>
+        <v>7022717</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3410,7 +3387,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3420,7 +3397,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3446,38 +3423,38 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071092</t>
+          <t>https://artportalen.se/Sighting/137071068</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>137071061</v>
+        <v>137071063</v>
       </c>
       <c r="B26" t="n">
-        <v>58008</v>
+        <v>79483</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3487,10 +3464,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>430511</v>
+        <v>430535</v>
       </c>
       <c r="R26" t="n">
-        <v>7022686</v>
+        <v>7022722</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3522,7 +3499,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3532,12 +3509,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3563,56 +3540,51 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071061</t>
+          <t>https://artportalen.se/Sighting/137071063</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>137071065</v>
+        <v>137071074</v>
       </c>
       <c r="B27" t="n">
-        <v>58008</v>
+        <v>79483</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Nygård, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>430555</v>
+        <v>430644</v>
       </c>
       <c r="R27" t="n">
-        <v>7022717</v>
+        <v>7022665</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3644,7 +3616,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3654,12 +3626,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3685,56 +3657,51 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071065</t>
+          <t>https://artportalen.se/Sighting/137071074</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>137071072</v>
+        <v>137071075</v>
       </c>
       <c r="B28" t="n">
-        <v>58008</v>
+        <v>79483</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Nygård, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>430593</v>
+        <v>430627</v>
       </c>
       <c r="R28" t="n">
-        <v>7022751</v>
+        <v>7022606</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3766,7 +3733,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3776,12 +3743,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3807,38 +3774,38 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071072</t>
+          <t>https://artportalen.se/Sighting/137071075</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>137071105</v>
+        <v>137071077</v>
       </c>
       <c r="B29" t="n">
-        <v>58008</v>
+        <v>79483</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3848,10 +3815,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>430742</v>
+        <v>430531</v>
       </c>
       <c r="R29" t="n">
-        <v>7022683</v>
+        <v>7022585</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3883,7 +3850,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3893,12 +3860,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3924,7 +3891,1185 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137071077</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>137071091</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79483</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Nygård, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>430703</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7022632</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Mörsil</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137071091</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>137071093</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79483</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Nygård, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>430735</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7022634</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Mörsil</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137071093</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>137133555</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79483</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Huug, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>430638</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7022751</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Mörsil</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137133555</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>137071076</v>
+      </c>
+      <c r="B33" t="n">
+        <v>58005</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Nygård, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>430579</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7022593</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Mörsil</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Hack</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137071076</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>137071092</v>
+      </c>
+      <c r="B34" t="n">
+        <v>58122</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100090</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Nötkråka</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Nucifraga caryocatactes</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Nygård, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>430711</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7022639</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Mörsil</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137071092</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>137071061</v>
+      </c>
+      <c r="B35" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Nygård, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>430511</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7022686</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Mörsil</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137071061</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>137071065</v>
+      </c>
+      <c r="B36" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Nygård, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>430555</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7022717</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Mörsil</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137071065</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>137071072</v>
+      </c>
+      <c r="B37" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Nygård, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>430593</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7022751</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Mörsil</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137071072</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>137071105</v>
+      </c>
+      <c r="B38" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Nygård, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>430742</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7022683</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Mörsil</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/137071105</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>137133552</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99368</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Huug, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>430566</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7022748</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Mörsil</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137133552</t>
         </is>
       </c>
     </row>
@@ -3958,6 +5103,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35493-2026 artfynd.xlsx
+++ b/artfynd/A 35493-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137071086</v>
       </c>
       <c r="B2" t="n">
-        <v>92120</v>
+        <v>92124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137071100</v>
       </c>
       <c r="B3" t="n">
-        <v>92120</v>
+        <v>92124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137071101</v>
       </c>
       <c r="B4" t="n">
-        <v>92120</v>
+        <v>92124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137071104</v>
       </c>
       <c r="B5" t="n">
-        <v>92120</v>
+        <v>92124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137133557</v>
       </c>
       <c r="B6" t="n">
-        <v>92120</v>
+        <v>92124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137133560</v>
       </c>
       <c r="B7" t="n">
-        <v>92120</v>
+        <v>92124</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137133561</v>
       </c>
       <c r="B8" t="n">
-        <v>92120</v>
+        <v>92124</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137133562</v>
       </c>
       <c r="B9" t="n">
-        <v>92120</v>
+        <v>92124</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>137071081</v>
       </c>
       <c r="B10" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>137071083</v>
       </c>
       <c r="B11" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>137071060</v>
       </c>
       <c r="B17" t="n">
-        <v>92351</v>
+        <v>92355</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>137133556</v>
       </c>
       <c r="B18" t="n">
-        <v>89485</v>
+        <v>89489</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
         <v>137071067</v>
       </c>
       <c r="B19" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>137071062</v>
       </c>
       <c r="B20" t="n">
-        <v>92120</v>
+        <v>92124</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>137071096</v>
       </c>
       <c r="B21" t="n">
-        <v>92120</v>
+        <v>92124</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>137071097</v>
       </c>
       <c r="B22" t="n">
-        <v>92120</v>
+        <v>92124</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>137071099</v>
       </c>
       <c r="B23" t="n">
-        <v>92120</v>
+        <v>92124</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>137133551</v>
       </c>
       <c r="B24" t="n">
-        <v>92120</v>
+        <v>92124</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>137071068</v>
       </c>
       <c r="B25" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>137071063</v>
       </c>
       <c r="B26" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>137071074</v>
       </c>
       <c r="B27" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>137071075</v>
       </c>
       <c r="B28" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         <v>137071077</v>
       </c>
       <c r="B29" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
         <v>137071091</v>
       </c>
       <c r="B30" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>137071093</v>
       </c>
       <c r="B31" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>137133555</v>
       </c>
       <c r="B32" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>137133552</v>
       </c>
       <c r="B39" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 35493-2026 artfynd.xlsx
+++ b/artfynd/A 35493-2026 artfynd.xlsx
@@ -4966,7 +4966,7 @@
         <v>137133552</v>
       </c>
       <c r="B39" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 35493-2026 artfynd.xlsx
+++ b/artfynd/A 35493-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137071086</v>
       </c>
       <c r="B2" t="n">
-        <v>92124</v>
+        <v>92126</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137071100</v>
       </c>
       <c r="B3" t="n">
-        <v>92124</v>
+        <v>92126</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137071101</v>
       </c>
       <c r="B4" t="n">
-        <v>92124</v>
+        <v>92126</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137071104</v>
       </c>
       <c r="B5" t="n">
-        <v>92124</v>
+        <v>92126</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137133557</v>
       </c>
       <c r="B6" t="n">
-        <v>92124</v>
+        <v>92126</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137133560</v>
       </c>
       <c r="B7" t="n">
-        <v>92124</v>
+        <v>92126</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137133561</v>
       </c>
       <c r="B8" t="n">
-        <v>92124</v>
+        <v>92126</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137133562</v>
       </c>
       <c r="B9" t="n">
-        <v>92124</v>
+        <v>92126</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>137071081</v>
       </c>
       <c r="B10" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>137071083</v>
       </c>
       <c r="B11" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>137071060</v>
       </c>
       <c r="B17" t="n">
-        <v>92355</v>
+        <v>92357</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>137133556</v>
       </c>
       <c r="B18" t="n">
-        <v>89489</v>
+        <v>89491</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
         <v>137071067</v>
       </c>
       <c r="B19" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>137071062</v>
       </c>
       <c r="B20" t="n">
-        <v>92124</v>
+        <v>92126</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>137071096</v>
       </c>
       <c r="B21" t="n">
-        <v>92124</v>
+        <v>92126</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>137071097</v>
       </c>
       <c r="B22" t="n">
-        <v>92124</v>
+        <v>92126</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>137071099</v>
       </c>
       <c r="B23" t="n">
-        <v>92124</v>
+        <v>92126</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>137133551</v>
       </c>
       <c r="B24" t="n">
-        <v>92124</v>
+        <v>92126</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>137071068</v>
       </c>
       <c r="B25" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>137071063</v>
       </c>
       <c r="B26" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>137071074</v>
       </c>
       <c r="B27" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>137071075</v>
       </c>
       <c r="B28" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         <v>137071077</v>
       </c>
       <c r="B29" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
         <v>137071091</v>
       </c>
       <c r="B30" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>137071093</v>
       </c>
       <c r="B31" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>137133555</v>
       </c>
       <c r="B32" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>137133552</v>
       </c>
       <c r="B39" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 35493-2026 artfynd.xlsx
+++ b/artfynd/A 35493-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137071086</v>
       </c>
       <c r="B2" t="n">
-        <v>92126</v>
+        <v>92139</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137071100</v>
       </c>
       <c r="B3" t="n">
-        <v>92126</v>
+        <v>92139</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137071101</v>
       </c>
       <c r="B4" t="n">
-        <v>92126</v>
+        <v>92139</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137071104</v>
       </c>
       <c r="B5" t="n">
-        <v>92126</v>
+        <v>92139</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137133557</v>
       </c>
       <c r="B6" t="n">
-        <v>92126</v>
+        <v>92139</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137133560</v>
       </c>
       <c r="B7" t="n">
-        <v>92126</v>
+        <v>92139</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137133561</v>
       </c>
       <c r="B8" t="n">
-        <v>92126</v>
+        <v>92139</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137133562</v>
       </c>
       <c r="B9" t="n">
-        <v>92126</v>
+        <v>92139</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>137071081</v>
       </c>
       <c r="B10" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>137071083</v>
       </c>
       <c r="B11" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>137071084</v>
       </c>
       <c r="B12" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         <v>137071087</v>
       </c>
       <c r="B13" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>137071090</v>
       </c>
       <c r="B14" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>137133565</v>
       </c>
       <c r="B15" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>137133566</v>
       </c>
       <c r="B16" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>137071060</v>
       </c>
       <c r="B17" t="n">
-        <v>92357</v>
+        <v>92370</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>137133556</v>
       </c>
       <c r="B18" t="n">
-        <v>89491</v>
+        <v>89504</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
         <v>137071067</v>
       </c>
       <c r="B19" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>137071062</v>
       </c>
       <c r="B20" t="n">
-        <v>92126</v>
+        <v>92139</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>137071096</v>
       </c>
       <c r="B21" t="n">
-        <v>92126</v>
+        <v>92139</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>137071097</v>
       </c>
       <c r="B22" t="n">
-        <v>92126</v>
+        <v>92139</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>137071099</v>
       </c>
       <c r="B23" t="n">
-        <v>92126</v>
+        <v>92139</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>137133551</v>
       </c>
       <c r="B24" t="n">
-        <v>92126</v>
+        <v>92139</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>137071068</v>
       </c>
       <c r="B25" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>137071063</v>
       </c>
       <c r="B26" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>137071074</v>
       </c>
       <c r="B27" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>137071075</v>
       </c>
       <c r="B28" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         <v>137071077</v>
       </c>
       <c r="B29" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
         <v>137071091</v>
       </c>
       <c r="B30" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>137071093</v>
       </c>
       <c r="B31" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>137133555</v>
       </c>
       <c r="B32" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4251,7 +4251,7 @@
         <v>137071076</v>
       </c>
       <c r="B33" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         <v>137071092</v>
       </c>
       <c r="B34" t="n">
-        <v>58122</v>
+        <v>58135</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>137071061</v>
       </c>
       <c r="B35" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>137071065</v>
       </c>
       <c r="B36" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         <v>137071072</v>
       </c>
       <c r="B37" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
         <v>137071105</v>
       </c>
       <c r="B38" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>137133552</v>
       </c>
       <c r="B39" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 35493-2026 artfynd.xlsx
+++ b/artfynd/A 35493-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137071086</v>
       </c>
       <c r="B2" t="n">
-        <v>92139</v>
+        <v>92141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137071100</v>
       </c>
       <c r="B3" t="n">
-        <v>92139</v>
+        <v>92141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137071101</v>
       </c>
       <c r="B4" t="n">
-        <v>92139</v>
+        <v>92141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137071104</v>
       </c>
       <c r="B5" t="n">
-        <v>92139</v>
+        <v>92141</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137133557</v>
       </c>
       <c r="B6" t="n">
-        <v>92139</v>
+        <v>92141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137133560</v>
       </c>
       <c r="B7" t="n">
-        <v>92139</v>
+        <v>92141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137133561</v>
       </c>
       <c r="B8" t="n">
-        <v>92139</v>
+        <v>92141</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137133562</v>
       </c>
       <c r="B9" t="n">
-        <v>92139</v>
+        <v>92141</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>137071081</v>
       </c>
       <c r="B10" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>137071083</v>
       </c>
       <c r="B11" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>137071084</v>
       </c>
       <c r="B12" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         <v>137071087</v>
       </c>
       <c r="B13" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>137071090</v>
       </c>
       <c r="B14" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>137133565</v>
       </c>
       <c r="B15" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>137133566</v>
       </c>
       <c r="B16" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>137071060</v>
       </c>
       <c r="B17" t="n">
-        <v>92370</v>
+        <v>92372</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>137133556</v>
       </c>
       <c r="B18" t="n">
-        <v>89504</v>
+        <v>89506</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
         <v>137071067</v>
       </c>
       <c r="B19" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>137071062</v>
       </c>
       <c r="B20" t="n">
-        <v>92139</v>
+        <v>92141</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>137071096</v>
       </c>
       <c r="B21" t="n">
-        <v>92139</v>
+        <v>92141</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>137071097</v>
       </c>
       <c r="B22" t="n">
-        <v>92139</v>
+        <v>92141</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>137071099</v>
       </c>
       <c r="B23" t="n">
-        <v>92139</v>
+        <v>92141</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>137133551</v>
       </c>
       <c r="B24" t="n">
-        <v>92139</v>
+        <v>92141</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>137071068</v>
       </c>
       <c r="B25" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>137071063</v>
       </c>
       <c r="B26" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>137071074</v>
       </c>
       <c r="B27" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>137071075</v>
       </c>
       <c r="B28" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         <v>137071077</v>
       </c>
       <c r="B29" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
         <v>137071091</v>
       </c>
       <c r="B30" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>137071093</v>
       </c>
       <c r="B31" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>137133555</v>
       </c>
       <c r="B32" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4251,7 +4251,7 @@
         <v>137071076</v>
       </c>
       <c r="B33" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         <v>137071092</v>
       </c>
       <c r="B34" t="n">
-        <v>58135</v>
+        <v>58137</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>137071061</v>
       </c>
       <c r="B35" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>137071065</v>
       </c>
       <c r="B36" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         <v>137071072</v>
       </c>
       <c r="B37" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
         <v>137071105</v>
       </c>
       <c r="B38" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>137133552</v>
       </c>
       <c r="B39" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 35493-2026 artfynd.xlsx
+++ b/artfynd/A 35493-2026 artfynd.xlsx
@@ -1844,11 +1844,7 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Nygård, Jmt</t>
@@ -1966,11 +1962,7 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Nygård, Jmt</t>
@@ -2088,11 +2080,7 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Nygård, Jmt</t>
@@ -2210,11 +2198,7 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Huug, Jmt</t>
@@ -4631,11 +4615,7 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Nygård, Jmt</t>
@@ -4753,11 +4733,7 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Nygård, Jmt</t>

--- a/artfynd/A 35493-2026 artfynd.xlsx
+++ b/artfynd/A 35493-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137071086</v>
       </c>
       <c r="B2" t="n">
-        <v>92141</v>
+        <v>92144</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137071100</v>
       </c>
       <c r="B3" t="n">
-        <v>92141</v>
+        <v>92144</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137071101</v>
       </c>
       <c r="B4" t="n">
-        <v>92141</v>
+        <v>92144</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137071104</v>
       </c>
       <c r="B5" t="n">
-        <v>92141</v>
+        <v>92144</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137133557</v>
       </c>
       <c r="B6" t="n">
-        <v>92141</v>
+        <v>92144</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137133560</v>
       </c>
       <c r="B7" t="n">
-        <v>92141</v>
+        <v>92144</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137133561</v>
       </c>
       <c r="B8" t="n">
-        <v>92141</v>
+        <v>92144</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137133562</v>
       </c>
       <c r="B9" t="n">
-        <v>92141</v>
+        <v>92144</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>137071060</v>
       </c>
       <c r="B17" t="n">
-        <v>92372</v>
+        <v>92375</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>137133556</v>
       </c>
       <c r="B18" t="n">
-        <v>89506</v>
+        <v>89509</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>137071067</v>
       </c>
       <c r="B19" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>137071062</v>
       </c>
       <c r="B20" t="n">
-        <v>92141</v>
+        <v>92144</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>137071096</v>
       </c>
       <c r="B21" t="n">
-        <v>92141</v>
+        <v>92144</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         <v>137071097</v>
       </c>
       <c r="B22" t="n">
-        <v>92141</v>
+        <v>92144</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>137071099</v>
       </c>
       <c r="B23" t="n">
-        <v>92141</v>
+        <v>92144</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         <v>137133551</v>
       </c>
       <c r="B24" t="n">
-        <v>92141</v>
+        <v>92144</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>137071068</v>
       </c>
       <c r="B25" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         <v>137133552</v>
       </c>
       <c r="B39" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 35493-2026 artfynd.xlsx
+++ b/artfynd/A 35493-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137071086</v>
       </c>
       <c r="B2" t="n">
-        <v>92144</v>
+        <v>92154</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137071100</v>
       </c>
       <c r="B3" t="n">
-        <v>92144</v>
+        <v>92154</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137071101</v>
       </c>
       <c r="B4" t="n">
-        <v>92144</v>
+        <v>92154</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137071104</v>
       </c>
       <c r="B5" t="n">
-        <v>92144</v>
+        <v>92154</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137133557</v>
       </c>
       <c r="B6" t="n">
-        <v>92144</v>
+        <v>92154</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137133560</v>
       </c>
       <c r="B7" t="n">
-        <v>92144</v>
+        <v>92154</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137133561</v>
       </c>
       <c r="B8" t="n">
-        <v>92144</v>
+        <v>92154</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137133562</v>
       </c>
       <c r="B9" t="n">
-        <v>92144</v>
+        <v>92154</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>137071081</v>
       </c>
       <c r="B10" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>137071083</v>
       </c>
       <c r="B11" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>137071084</v>
       </c>
       <c r="B12" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>137071087</v>
       </c>
       <c r="B13" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>137071090</v>
       </c>
       <c r="B14" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>137133565</v>
       </c>
       <c r="B15" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>137133566</v>
       </c>
       <c r="B16" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>137071060</v>
       </c>
       <c r="B17" t="n">
-        <v>92375</v>
+        <v>92385</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>137133556</v>
       </c>
       <c r="B18" t="n">
-        <v>89509</v>
+        <v>89519</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>137071067</v>
       </c>
       <c r="B19" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>137071062</v>
       </c>
       <c r="B20" t="n">
-        <v>92144</v>
+        <v>92154</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>137071096</v>
       </c>
       <c r="B21" t="n">
-        <v>92144</v>
+        <v>92154</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         <v>137071097</v>
       </c>
       <c r="B22" t="n">
-        <v>92144</v>
+        <v>92154</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>137071099</v>
       </c>
       <c r="B23" t="n">
-        <v>92144</v>
+        <v>92154</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         <v>137133551</v>
       </c>
       <c r="B24" t="n">
-        <v>92144</v>
+        <v>92154</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>137071068</v>
       </c>
       <c r="B25" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>137071063</v>
       </c>
       <c r="B26" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         <v>137071074</v>
       </c>
       <c r="B27" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>137071075</v>
       </c>
       <c r="B28" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>137071077</v>
       </c>
       <c r="B29" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>137071091</v>
       </c>
       <c r="B30" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>137071093</v>
       </c>
       <c r="B31" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>137133555</v>
       </c>
       <c r="B32" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         <v>137071076</v>
       </c>
       <c r="B33" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>137071092</v>
       </c>
       <c r="B34" t="n">
-        <v>58137</v>
+        <v>58147</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         <v>137071061</v>
       </c>
       <c r="B35" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         <v>137071065</v>
       </c>
       <c r="B36" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         <v>137071072</v>
       </c>
       <c r="B37" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>137071105</v>
       </c>
       <c r="B38" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         <v>137133552</v>
       </c>
       <c r="B39" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 35493-2026 artfynd.xlsx
+++ b/artfynd/A 35493-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137071086</v>
       </c>
       <c r="B2" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137071100</v>
       </c>
       <c r="B3" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137071101</v>
       </c>
       <c r="B4" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137071104</v>
       </c>
       <c r="B5" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137133557</v>
       </c>
       <c r="B6" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137133560</v>
       </c>
       <c r="B7" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137133561</v>
       </c>
       <c r="B8" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137133562</v>
       </c>
       <c r="B9" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>137071060</v>
       </c>
       <c r="B17" t="n">
-        <v>92385</v>
+        <v>92386</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>137133556</v>
       </c>
       <c r="B18" t="n">
-        <v>89519</v>
+        <v>89520</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>137071067</v>
       </c>
       <c r="B19" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>137071062</v>
       </c>
       <c r="B20" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>137071096</v>
       </c>
       <c r="B21" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         <v>137071097</v>
       </c>
       <c r="B22" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>137071099</v>
       </c>
       <c r="B23" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         <v>137133551</v>
       </c>
       <c r="B24" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>137071068</v>
       </c>
       <c r="B25" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         <v>137133552</v>
       </c>
       <c r="B39" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 35493-2026 artfynd.xlsx
+++ b/artfynd/A 35493-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137071086</v>
       </c>
       <c r="B2" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137071100</v>
       </c>
       <c r="B3" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137071101</v>
       </c>
       <c r="B4" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137071104</v>
       </c>
       <c r="B5" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137133557</v>
       </c>
       <c r="B6" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137133560</v>
       </c>
       <c r="B7" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137133561</v>
       </c>
       <c r="B8" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137133562</v>
       </c>
       <c r="B9" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>137071081</v>
       </c>
       <c r="B10" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>137071083</v>
       </c>
       <c r="B11" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>137071084</v>
       </c>
       <c r="B12" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>137071087</v>
       </c>
       <c r="B13" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>137071090</v>
       </c>
       <c r="B14" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>137133565</v>
       </c>
       <c r="B15" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>137133566</v>
       </c>
       <c r="B16" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>137071060</v>
       </c>
       <c r="B17" t="n">
-        <v>92386</v>
+        <v>92389</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>137133556</v>
       </c>
       <c r="B18" t="n">
-        <v>89520</v>
+        <v>89523</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>137071067</v>
       </c>
       <c r="B19" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>137071062</v>
       </c>
       <c r="B20" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>137071096</v>
       </c>
       <c r="B21" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         <v>137071097</v>
       </c>
       <c r="B22" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>137071099</v>
       </c>
       <c r="B23" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         <v>137133551</v>
       </c>
       <c r="B24" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>137071068</v>
       </c>
       <c r="B25" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>137071063</v>
       </c>
       <c r="B26" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         <v>137071074</v>
       </c>
       <c r="B27" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>137071075</v>
       </c>
       <c r="B28" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>137071077</v>
       </c>
       <c r="B29" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>137071091</v>
       </c>
       <c r="B30" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>137071093</v>
       </c>
       <c r="B31" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>137133555</v>
       </c>
       <c r="B32" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         <v>137071076</v>
       </c>
       <c r="B33" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>137071092</v>
       </c>
       <c r="B34" t="n">
-        <v>58147</v>
+        <v>58148</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         <v>137071061</v>
       </c>
       <c r="B35" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         <v>137071065</v>
       </c>
       <c r="B36" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         <v>137071072</v>
       </c>
       <c r="B37" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>137071105</v>
       </c>
       <c r="B38" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         <v>137133552</v>
       </c>
       <c r="B39" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 35493-2026 artfynd.xlsx
+++ b/artfynd/A 35493-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137071086</v>
       </c>
       <c r="B2" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137071100</v>
       </c>
       <c r="B3" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137071101</v>
       </c>
       <c r="B4" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137071104</v>
       </c>
       <c r="B5" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137133557</v>
       </c>
       <c r="B6" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137133560</v>
       </c>
       <c r="B7" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137133561</v>
       </c>
       <c r="B8" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137133562</v>
       </c>
       <c r="B9" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>137071060</v>
       </c>
       <c r="B17" t="n">
-        <v>92389</v>
+        <v>92391</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>137071067</v>
       </c>
       <c r="B19" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>137071062</v>
       </c>
       <c r="B20" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>137071096</v>
       </c>
       <c r="B21" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         <v>137071097</v>
       </c>
       <c r="B22" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>137071099</v>
       </c>
       <c r="B23" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         <v>137133551</v>
       </c>
       <c r="B24" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>137071068</v>
       </c>
       <c r="B25" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         <v>137133552</v>
       </c>
       <c r="B39" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 35493-2026 artfynd.xlsx
+++ b/artfynd/A 35493-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137071086</v>
       </c>
       <c r="B2" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137071100</v>
       </c>
       <c r="B3" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137071101</v>
       </c>
       <c r="B4" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137071104</v>
       </c>
       <c r="B5" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137133557</v>
       </c>
       <c r="B6" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137133560</v>
       </c>
       <c r="B7" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137133561</v>
       </c>
       <c r="B8" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137133562</v>
       </c>
       <c r="B9" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>137071081</v>
       </c>
       <c r="B10" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>137071083</v>
       </c>
       <c r="B11" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>137071084</v>
       </c>
       <c r="B12" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>137071087</v>
       </c>
       <c r="B13" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>137071090</v>
       </c>
       <c r="B14" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>137133565</v>
       </c>
       <c r="B15" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>137133566</v>
       </c>
       <c r="B16" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>137071060</v>
       </c>
       <c r="B17" t="n">
-        <v>92391</v>
+        <v>92396</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>137133556</v>
       </c>
       <c r="B18" t="n">
-        <v>89523</v>
+        <v>89528</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>137071067</v>
       </c>
       <c r="B19" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>137071062</v>
       </c>
       <c r="B20" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>137071096</v>
       </c>
       <c r="B21" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         <v>137071097</v>
       </c>
       <c r="B22" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>137071099</v>
       </c>
       <c r="B23" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         <v>137133551</v>
       </c>
       <c r="B24" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>137071068</v>
       </c>
       <c r="B25" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>137071063</v>
       </c>
       <c r="B26" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         <v>137071074</v>
       </c>
       <c r="B27" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>137071075</v>
       </c>
       <c r="B28" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>137071077</v>
       </c>
       <c r="B29" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>137071091</v>
       </c>
       <c r="B30" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>137071093</v>
       </c>
       <c r="B31" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>137133555</v>
       </c>
       <c r="B32" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         <v>137071076</v>
       </c>
       <c r="B33" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>137071092</v>
       </c>
       <c r="B34" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         <v>137071061</v>
       </c>
       <c r="B35" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         <v>137071065</v>
       </c>
       <c r="B36" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         <v>137071072</v>
       </c>
       <c r="B37" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>137071105</v>
       </c>
       <c r="B38" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         <v>137133552</v>
       </c>
       <c r="B39" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 35493-2026 artfynd.xlsx
+++ b/artfynd/A 35493-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137071086</v>
       </c>
       <c r="B2" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137071100</v>
       </c>
       <c r="B3" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137071101</v>
       </c>
       <c r="B4" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137071104</v>
       </c>
       <c r="B5" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137133557</v>
       </c>
       <c r="B6" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137133560</v>
       </c>
       <c r="B7" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137133561</v>
       </c>
       <c r="B8" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137133562</v>
       </c>
       <c r="B9" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>137071081</v>
       </c>
       <c r="B10" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>137071083</v>
       </c>
       <c r="B11" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>137071060</v>
       </c>
       <c r="B17" t="n">
-        <v>92396</v>
+        <v>92408</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>137133556</v>
       </c>
       <c r="B18" t="n">
-        <v>89528</v>
+        <v>89539</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>137071067</v>
       </c>
       <c r="B19" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>137071062</v>
       </c>
       <c r="B20" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>137071096</v>
       </c>
       <c r="B21" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         <v>137071097</v>
       </c>
       <c r="B22" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>137071099</v>
       </c>
       <c r="B23" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         <v>137133551</v>
       </c>
       <c r="B24" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>137071068</v>
       </c>
       <c r="B25" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>137071063</v>
       </c>
       <c r="B26" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         <v>137071074</v>
       </c>
       <c r="B27" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>137071075</v>
       </c>
       <c r="B28" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>137071077</v>
       </c>
       <c r="B29" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>137071091</v>
       </c>
       <c r="B30" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>137071093</v>
       </c>
       <c r="B31" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>137133555</v>
       </c>
       <c r="B32" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         <v>137133552</v>
       </c>
       <c r="B39" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 35493-2026 artfynd.xlsx
+++ b/artfynd/A 35493-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137071086</v>
       </c>
       <c r="B2" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137071100</v>
       </c>
       <c r="B3" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137071101</v>
       </c>
       <c r="B4" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137071104</v>
       </c>
       <c r="B5" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137133557</v>
       </c>
       <c r="B6" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137133560</v>
       </c>
       <c r="B7" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137133561</v>
       </c>
       <c r="B8" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137133562</v>
       </c>
       <c r="B9" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>137071081</v>
       </c>
       <c r="B10" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>137071083</v>
       </c>
       <c r="B11" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>137071060</v>
       </c>
       <c r="B17" t="n">
-        <v>92408</v>
+        <v>92409</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>137133556</v>
       </c>
       <c r="B18" t="n">
-        <v>89539</v>
+        <v>89540</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>137071067</v>
       </c>
       <c r="B19" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>137071062</v>
       </c>
       <c r="B20" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>137071096</v>
       </c>
       <c r="B21" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         <v>137071097</v>
       </c>
       <c r="B22" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>137071099</v>
       </c>
       <c r="B23" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         <v>137133551</v>
       </c>
       <c r="B24" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>137071068</v>
       </c>
       <c r="B25" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>137071063</v>
       </c>
       <c r="B26" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         <v>137071074</v>
       </c>
       <c r="B27" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>137071075</v>
       </c>
       <c r="B28" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>137071077</v>
       </c>
       <c r="B29" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>137071091</v>
       </c>
       <c r="B30" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>137071093</v>
       </c>
       <c r="B31" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>137133555</v>
       </c>
       <c r="B32" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         <v>137133552</v>
       </c>
       <c r="B39" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 35493-2026 artfynd.xlsx
+++ b/artfynd/A 35493-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137071086</v>
       </c>
       <c r="B2" t="n">
-        <v>92178</v>
+        <v>92181</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137071100</v>
       </c>
       <c r="B3" t="n">
-        <v>92178</v>
+        <v>92181</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137071101</v>
       </c>
       <c r="B4" t="n">
-        <v>92178</v>
+        <v>92181</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137071104</v>
       </c>
       <c r="B5" t="n">
-        <v>92178</v>
+        <v>92181</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137133557</v>
       </c>
       <c r="B6" t="n">
-        <v>92178</v>
+        <v>92181</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137133560</v>
       </c>
       <c r="B7" t="n">
-        <v>92178</v>
+        <v>92181</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137133561</v>
       </c>
       <c r="B8" t="n">
-        <v>92178</v>
+        <v>92181</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137133562</v>
       </c>
       <c r="B9" t="n">
-        <v>92178</v>
+        <v>92181</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>137071081</v>
       </c>
       <c r="B10" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>137071083</v>
       </c>
       <c r="B11" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>137071060</v>
       </c>
       <c r="B17" t="n">
-        <v>92409</v>
+        <v>92412</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>137133556</v>
       </c>
       <c r="B18" t="n">
-        <v>89540</v>
+        <v>89543</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>137071067</v>
       </c>
       <c r="B19" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>137071062</v>
       </c>
       <c r="B20" t="n">
-        <v>92178</v>
+        <v>92181</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>137071096</v>
       </c>
       <c r="B21" t="n">
-        <v>92178</v>
+        <v>92181</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         <v>137071097</v>
       </c>
       <c r="B22" t="n">
-        <v>92178</v>
+        <v>92181</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>137071099</v>
       </c>
       <c r="B23" t="n">
-        <v>92178</v>
+        <v>92181</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         <v>137133551</v>
       </c>
       <c r="B24" t="n">
-        <v>92178</v>
+        <v>92181</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>137071068</v>
       </c>
       <c r="B25" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>137071063</v>
       </c>
       <c r="B26" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         <v>137071074</v>
       </c>
       <c r="B27" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>137071075</v>
       </c>
       <c r="B28" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>137071077</v>
       </c>
       <c r="B29" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>137071091</v>
       </c>
       <c r="B30" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>137071093</v>
       </c>
       <c r="B31" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>137133555</v>
       </c>
       <c r="B32" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         <v>137133552</v>
       </c>
       <c r="B39" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 35493-2026 artfynd.xlsx
+++ b/artfynd/A 35493-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137071086</v>
       </c>
       <c r="B2" t="n">
-        <v>92181</v>
+        <v>92185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137071100</v>
       </c>
       <c r="B3" t="n">
-        <v>92181</v>
+        <v>92185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137071101</v>
       </c>
       <c r="B4" t="n">
-        <v>92181</v>
+        <v>92185</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137071104</v>
       </c>
       <c r="B5" t="n">
-        <v>92181</v>
+        <v>92185</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137133557</v>
       </c>
       <c r="B6" t="n">
-        <v>92181</v>
+        <v>92185</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137133560</v>
       </c>
       <c r="B7" t="n">
-        <v>92181</v>
+        <v>92185</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137133561</v>
       </c>
       <c r="B8" t="n">
-        <v>92181</v>
+        <v>92185</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137133562</v>
       </c>
       <c r="B9" t="n">
-        <v>92181</v>
+        <v>92185</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>137071081</v>
       </c>
       <c r="B10" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>137071083</v>
       </c>
       <c r="B11" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>137071084</v>
       </c>
       <c r="B12" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>137071087</v>
       </c>
       <c r="B13" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>137071090</v>
       </c>
       <c r="B14" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>137133565</v>
       </c>
       <c r="B15" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>137133566</v>
       </c>
       <c r="B16" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>137071060</v>
       </c>
       <c r="B17" t="n">
-        <v>92412</v>
+        <v>92416</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>137133556</v>
       </c>
       <c r="B18" t="n">
-        <v>89543</v>
+        <v>89547</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>137071067</v>
       </c>
       <c r="B19" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>137071062</v>
       </c>
       <c r="B20" t="n">
-        <v>92181</v>
+        <v>92185</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>137071096</v>
       </c>
       <c r="B21" t="n">
-        <v>92181</v>
+        <v>92185</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         <v>137071097</v>
       </c>
       <c r="B22" t="n">
-        <v>92181</v>
+        <v>92185</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>137071099</v>
       </c>
       <c r="B23" t="n">
-        <v>92181</v>
+        <v>92185</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         <v>137133551</v>
       </c>
       <c r="B24" t="n">
-        <v>92181</v>
+        <v>92185</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>137071068</v>
       </c>
       <c r="B25" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>137071063</v>
       </c>
       <c r="B26" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         <v>137071074</v>
       </c>
       <c r="B27" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>137071075</v>
       </c>
       <c r="B28" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>137071077</v>
       </c>
       <c r="B29" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>137071091</v>
       </c>
       <c r="B30" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>137071093</v>
       </c>
       <c r="B31" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>137133555</v>
       </c>
       <c r="B32" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         <v>137071076</v>
       </c>
       <c r="B33" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>137071092</v>
       </c>
       <c r="B34" t="n">
-        <v>58149</v>
+        <v>58152</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         <v>137071061</v>
       </c>
       <c r="B35" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         <v>137071065</v>
       </c>
       <c r="B36" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         <v>137071072</v>
       </c>
       <c r="B37" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>137071105</v>
       </c>
       <c r="B38" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         <v>137133552</v>
       </c>
       <c r="B39" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
